--- a/data/evaluation/retrieval_results.xlsx
+++ b/data/evaluation/retrieval_results.xlsx
@@ -904,12 +904,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：China + 1 战略（多地区混合布局） - Evidence ID: PLUS1_003 Title: 比亚迪 BYD：China + 1 战略（多地区混合布局） Publisher: 凤...</t>
+          <t>比亚迪 BYD：China + 1 战略（多地区混合布局） - Evidence ID: PLUS1_003 Title: 比亚迪 BYD：China + 1 战略（多地区混合布局） Publisher: A...</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>ANTARA（印尼国家通讯社）</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提...</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） ...</t>
+          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>澎湃新闻</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publis...</t>
+          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） ...</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>澎湃新闻 / 盖世汽车社区</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2305,14 +2305,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RELOC_004</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提...</t>
+          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publis...</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>新浪财经</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：欧洲销售疲软 + 经济挑战 + ...</t>
+          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>澎湃新闻</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - ## 二、决策触发（Decision Trigger） 触发类型：cost_change（成本变化） 触发细节：欧洲销售疲软 + 经济挑战 + ...</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>RETURN_004</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -6540,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6559,12 +6559,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>36氪 / 财新网</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6574,11 +6574,11 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>PLUS1_005</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -8184,26 +8184,26 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>三星电子 Samsung Electronics：China + 1 战略（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：半导体与消费电子产能分布在中国（西安 NAND、苏州封测）、韩国、越南（手...</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>新浪财经 / 东方财富网</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8249,26 +8249,26 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK +...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：苹果产品组装以中国大陆为核心，印度、越南为分散地。 主要市场：全球。 供应...</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
+          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>东方财富网 / 腾讯新闻</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
+          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>澎湃新闻 / 盖世汽车社区</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O263" t="n">
         <v>1</v>
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>RELOC_001</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -18565,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -18584,12 +18584,12 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华电动车加征关税、...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：苹果产品组装以中国大陆为核心，印度、越南为分散地。 主要市场：全球。 供应...</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>东方财富网（转比亚迪官方）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_001</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -18630,7 +18630,7 @@
         <v>1</v>
       </c>
       <c r="E280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -18649,12 +18649,12 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华加征关税及客户'...</t>
+          <t>比亚迪 BYD：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华电动车加征关税、...</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>东方财富网（转比亚迪官方）</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -18664,11 +18664,11 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N280" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -18685,17 +18685,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="C281" t="n">
         <v>10</v>
       </c>
       <c r="D281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -18714,22 +18714,22 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华加征关税及客户'...</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>东方财富网 / 腾讯新闻</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N281" t="n">
@@ -18739,7 +18739,7 @@
         <v>0</v>
       </c>
       <c r="P281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RETURN_002; RELOC_002; RELOC_005</t>
+          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RELOC_005</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20379,7 +20379,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -20518,7 +20518,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001; RELOC_001; RELOC_004; RETURN_004; RELOC_006; RELOC_002</t>
+          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001; RELOC_001; RELOC_004; RELOC_006; RETURN_004; RELOC_002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_001; RETURN_004; RELOC_006; RELOC_002</t>
+          <t>RELOC_005; RELOC_001; RELOC_006; RETURN_004; RELOC_002</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_004; RETURN_001; CASE_010; RELOC_005; RELOC_001; PLUS1_002; RELOC_007; RELOC_003; WH_002</t>
+          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005; RELOC_001; PLUS1_002; RELOC_007; RELOC_003; WH_002</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>RETURN_004; RETURN_001; PLUS1_002; RELOC_007; RELOC_003</t>
+          <t>RETURN_001; RETURN_004; PLUS1_002; RELOC_007; RELOC_003</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_003; RELOC_005; WH_002; RETURN_004; RELOC_008; RELOC_002; RELOC_004; RELOC_001</t>
+          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002; RETURN_004; RELOC_008; RELOC_002; RELOC_004; RELOC_001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -22321,12 +22321,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; CASE_010; RELOC_001; RELOC_005; CSIS_001</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; CASE_010; RETURN_002; RELOC_001; RELOC_005</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; CASE_010; CSIS_001; TRD_003; WH_002</t>
+          <t>CASE_002; CASE_003; CASE_010; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -22336,7 +22336,7 @@
         <v>0.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -22348,10 +22348,10 @@
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -22360,11 +22360,11 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; CSIS_001</t>
+          <t>DOC_001; CASE_003</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.854</v>
+        <v>0.858</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>0.78 / 0.925 / 5</t>
+          <t>0.747 / 0.938 / 5</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/retrieval_results.xlsx
+++ b/data/evaluation/retrieval_results.xlsx
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1164,22 +1164,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - The State Council of the People’s Republic of China. 19 February. MOFCOM...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2399,26 +2399,26 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -2435,14 +2435,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -2464,26 +2464,26 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -2890,17 +2890,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2919,26 +2919,26 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2984,26 +2984,26 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -3605,14 +3605,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -3634,26 +3634,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3699,26 +3699,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -3735,17 +3735,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3764,26 +3764,26 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 17 - Ⅱ、两用物项和技术出口许可证管理目录 一、两用物项出口管制清单所列物项 （一）专用材料和相关设备、化学制品、微生物和毒素 1A 系...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3978,13 +3978,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4154,17 +4154,17 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -4265,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4284,26 +4284,26 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -4320,14 +4320,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -4349,17 +4349,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4414,26 +4414,26 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4999,26 +4999,26 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -5035,14 +5035,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -5064,17 +5064,17 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Trade Representative has determined to: modify the actions being taken i...</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5408,13 +5408,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -5425,14 +5425,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -5454,17 +5454,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5473,13 +5473,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5490,14 +5490,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -5519,26 +5519,26 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - 18 World Investment Report 2026 International Investment in a Turbulent ...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - For decades, paper documentation and a border check were enough. Supply ...</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - For decades, paper documentation and a border check were enough. Supply ...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -5620,14 +5620,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -5649,17 +5649,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 44 - 序号 管制编码 物项名称及描述 参考商品名称 海关商品编号 单位 乙 酯 （ CAS 2387496-06-0） 基氟磷酸甲酯 N...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - 91. 04 applies to facemasks of textiles, disposable, of China, described...</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5685,14 +5685,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -5714,17 +5714,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - However, as trade volumes surged, supply chains became more complicated,...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Current consolidated version: 11/02/2026 ELI: Language BG ES CS DA DE ET...</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -6104,22 +6104,22 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -6169,26 +6169,26 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -6280,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -6299,26 +6299,26 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -6345,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -6364,26 +6364,26 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -6559,26 +6559,26 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -6670,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6689,26 +6689,26 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -6735,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6754,22 +6754,22 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -6855,17 +6855,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>8</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6884,26 +6884,26 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 61 - 2B 测试、检测和生产设备 序号 管制编码 物项名称及描述 参考商品名称 海关商品编号 单位 394 2B005 具有以下两种特性...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6949,26 +6949,26 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7014,17 +7014,17 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - cn/en/3688253/3689009/4180845/4821853/2023031716595159517. pdf https://w...</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7094,11 +7094,11 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7159,11 +7159,11 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O104" t="n">
         <v>1</v>
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7274,26 +7274,26 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research A...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O105" t="n">
         <v>1</v>
@@ -7310,17 +7310,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7339,26 +7339,26 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Once leaders have defined their objectives, they can choose from a tool ...</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -7404,26 +7404,26 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -7469,26 +7469,26 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -7534,26 +7534,26 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - GLOBAL TRADE OUTLOOK AND STATISTICS - MARCH 2026 40 Bibliography Abbas, ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8119,26 +8119,26 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - cn/en/3688253/3689009/4180845/4821853/2023031716595159517. pdf https://w...</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8249,22 +8249,22 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="O123" t="n">
         <v>1</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8589,11 +8589,11 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
@@ -8704,26 +8704,26 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -8834,26 +8834,26 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -8870,17 +8870,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>9</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -8899,22 +8899,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O133" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O135" t="n">
         <v>1</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -9549,26 +9549,26 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O146" t="n">
         <v>1</v>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -10069,17 +10069,17 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -10170,14 +10170,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -10199,17 +10199,17 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - However, as trade volumes surged, supply chains became more complicated,...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -10235,14 +10235,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>10</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -10264,17 +10264,17 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - 1484 that a foreign IOR: (1) may not rely on a continuous bond to meet t...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="O152" t="n">
         <v>1</v>
@@ -10365,14 +10365,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -10394,32 +10394,32 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O153" t="n">
         <v>1</v>
       </c>
       <c r="P153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -10459,26 +10459,26 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
@@ -10495,14 +10495,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -10524,7 +10524,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10543,13 +10543,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -10560,14 +10560,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>5</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>2</v>
@@ -10589,17 +10589,17 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -10784,26 +10784,26 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Chapter III International Investment in a Turbulent Era: Trends and poli...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -11063,7 +11063,7 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O163" t="n">
         <v>1</v>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O164" t="n">
         <v>1</v>
@@ -11145,14 +11145,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>2</v>
@@ -11174,32 +11174,32 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O165" t="n">
         <v>1</v>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -11210,14 +11210,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>2</v>
@@ -11239,12 +11239,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -11254,17 +11254,17 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="O166" t="n">
         <v>1</v>
       </c>
       <c r="P166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -11304,26 +11304,26 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -11369,26 +11369,26 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Chapter I International investment trends 21 Asian technology firms also...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -11415,7 +11415,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -11434,26 +11434,26 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N169" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -11499,17 +11499,17 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -11518,7 +11518,7 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -11535,14 +11535,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>10</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>2</v>
@@ -11564,17 +11564,17 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -11629,26 +11629,26 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O172" t="n">
         <v>1</v>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -11694,26 +11694,26 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O173" t="n">
         <v>1</v>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O174" t="n">
         <v>1</v>
@@ -11795,17 +11795,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C175" t="n">
         <v>4</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -11824,32 +11824,32 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O175" t="n">
         <v>1</v>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -11860,17 +11860,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>5</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -11889,32 +11889,32 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O176" t="n">
         <v>1</v>
       </c>
       <c r="P176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -11954,17 +11954,17 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -11990,14 +11990,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
         <v>2</v>
@@ -12019,26 +12019,26 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -12055,14 +12055,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>8</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -12084,26 +12084,26 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -12120,14 +12120,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>2</v>
@@ -12149,26 +12149,26 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O182" t="n">
         <v>1</v>
@@ -12363,7 +12363,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O183" t="n">
         <v>1</v>
@@ -12445,17 +12445,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C185" t="n">
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -12474,32 +12474,32 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O185" t="n">
         <v>1</v>
       </c>
       <c r="P185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -12510,17 +12510,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>5</v>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -12539,32 +12539,32 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O186" t="n">
         <v>1</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -12864,17 +12864,17 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="O192" t="n">
         <v>1</v>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O193" t="n">
         <v>1</v>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="O194" t="n">
         <v>1</v>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O195" t="n">
         <v>1</v>
@@ -13160,14 +13160,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C196" t="n">
         <v>5</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" t="n">
         <v>2</v>
@@ -13189,32 +13189,32 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O196" t="n">
         <v>1</v>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -13290,14 +13290,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>7</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
         <v>2</v>
@@ -13319,32 +13319,32 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - The total decline in the value of exports to the United States in 2025 w...</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -13355,14 +13355,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C199" t="n">
         <v>8</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E199" t="n">
         <v>2</v>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - On the recipient side, the United States, the European Union and China, ...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -13420,14 +13420,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C200" t="n">
         <v>9</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
         <v>2</v>
@@ -13449,26 +13449,26 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13533,7 +13533,7 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O202" t="n">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O203" t="n">
         <v>1</v>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="O204" t="n">
         <v>1</v>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O205" t="n">
         <v>1</v>
@@ -13858,7 +13858,7 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O206" t="n">
         <v>1</v>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -13904,26 +13904,26 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N207" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -13969,26 +13969,26 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N208" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -14099,26 +14099,26 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - These differences confirm that strategic sector investment cannot be add...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O212" t="n">
         <v>1</v>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O213" t="n">
         <v>1</v>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O214" t="n">
         <v>1</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -14424,17 +14424,17 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O215" t="n">
         <v>1</v>
@@ -14460,14 +14460,14 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C216" t="n">
         <v>5</v>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
         <v>2</v>
@@ -14489,17 +14489,17 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - -154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -14525,14 +14525,14 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C217" t="n">
         <v>6</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
         <v>2</v>
@@ -14554,17 +14554,17 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -14590,17 +14590,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C218" t="n">
         <v>7</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -14619,22 +14619,22 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -14684,17 +14684,17 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -14720,17 +14720,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C220" t="n">
         <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -14749,26 +14749,26 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -14795,7 +14795,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -14814,26 +14814,26 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N221" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14898,7 +14898,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O222" t="n">
         <v>1</v>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -14944,12 +14944,12 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O223" t="n">
         <v>1</v>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O224" t="n">
         <v>1</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -15074,12 +15074,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -15093,7 +15093,7 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="O225" t="n">
         <v>1</v>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -15139,12 +15139,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -15158,7 +15158,7 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="O226" t="n">
         <v>1</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -15305,14 +15305,14 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
         <v>2</v>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N229" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O232" t="n">
         <v>1</v>
@@ -15613,7 +15613,7 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O233" t="n">
         <v>1</v>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O234" t="n">
         <v>1</v>
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O235" t="n">
         <v>1</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O236" t="n">
         <v>1</v>
@@ -15825,17 +15825,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C237" t="n">
         <v>6</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -15854,32 +15854,32 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N237" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -15890,17 +15890,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C238" t="n">
         <v>7</v>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -15919,32 +15919,32 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
       </c>
       <c r="P238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -15955,14 +15955,14 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C239" t="n">
         <v>8</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
         <v>2</v>
@@ -15984,17 +15984,17 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -16020,17 +16020,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C240" t="n">
         <v>9</v>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -16049,26 +16049,26 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -16085,17 +16085,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C241" t="n">
         <v>10</v>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -16114,26 +16114,26 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="O242" t="n">
         <v>1</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O243" t="n">
         <v>1</v>
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O244" t="n">
         <v>1</v>
@@ -16345,7 +16345,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -16389,11 +16389,11 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="O245" t="n">
         <v>1</v>
@@ -16410,14 +16410,14 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C246" t="n">
         <v>5</v>
       </c>
       <c r="D246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
         <v>2</v>
@@ -16439,32 +16439,32 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O246" t="n">
         <v>1</v>
       </c>
       <c r="P246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -16475,14 +16475,14 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C247" t="n">
         <v>6</v>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
         <v>2</v>
@@ -16504,32 +16504,32 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -16540,14 +16540,14 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C248" t="n">
         <v>7</v>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" t="n">
         <v>2</v>
@@ -16569,26 +16569,26 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -16745,7 +16745,7 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -16764,26 +16764,26 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O252" t="n">
         <v>1</v>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O253" t="n">
         <v>1</v>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O254" t="n">
         <v>1</v>
@@ -16995,17 +16995,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C255" t="n">
         <v>4</v>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -17024,32 +17024,32 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N255" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O255" t="n">
         <v>1</v>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -17060,17 +17060,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C256" t="n">
         <v>5</v>
       </c>
       <c r="D256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -17089,22 +17089,22 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N256" t="n">
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -17255,14 +17255,14 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C259" t="n">
         <v>8</v>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
         <v>2</v>
@@ -17284,26 +17284,26 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N259" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -17320,14 +17320,14 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C260" t="n">
         <v>9</v>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
         <v>2</v>
@@ -17349,17 +17349,17 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -17368,7 +17368,7 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -17385,14 +17385,14 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C261" t="n">
         <v>10</v>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261" t="n">
         <v>2</v>
@@ -17414,17 +17414,17 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 60 - （二）材料加工 2A 系统、设备和部件 序号 管制编码 物项名称及描述 参考商品名称 海关商品编号 单位 387 2A225. a...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -17479,12 +17479,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -17498,7 +17498,7 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O262" t="n">
         <v>1</v>
@@ -17515,7 +17515,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="O263" t="n">
         <v>1</v>
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O265" t="n">
         <v>1</v>
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="O266" t="n">
         <v>1</v>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -17804,26 +17804,26 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -17869,26 +17869,26 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -18045,7 +18045,7 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -18064,26 +18064,26 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N271" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -18148,7 +18148,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="O272" t="n">
         <v>1</v>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -18194,17 +18194,17 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -18213,7 +18213,7 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O273" t="n">
         <v>1</v>
@@ -18230,14 +18230,14 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C274" t="n">
         <v>3</v>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E274" t="n">
         <v>2</v>
@@ -18259,12 +18259,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18278,13 +18278,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O274" t="n">
         <v>1</v>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -18324,17 +18324,17 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -18343,7 +18343,7 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O275" t="n">
         <v>1</v>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -18389,17 +18389,17 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O276" t="n">
         <v>1</v>
@@ -18425,14 +18425,14 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C277" t="n">
         <v>6</v>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E277" t="n">
         <v>2</v>
@@ -18454,17 +18454,17 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -18473,13 +18473,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
       </c>
       <c r="P277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -18538,7 +18538,7 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -18555,7 +18555,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -18584,26 +18584,26 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -18649,26 +18649,26 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N280" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -18685,17 +18685,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C281" t="n">
         <v>10</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -18714,26 +18714,26 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - These issues have featured prominently in policy discussions at Minister...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N281" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="O282" t="n">
         <v>1</v>
@@ -18815,14 +18815,14 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C283" t="n">
         <v>2</v>
       </c>
       <c r="D283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E283" t="n">
         <v>2</v>
@@ -18844,17 +18844,17 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -18863,13 +18863,13 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="O283" t="n">
         <v>1</v>
       </c>
       <c r="P283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -18880,14 +18880,14 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C284" t="n">
         <v>3</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E284" t="n">
         <v>2</v>
@@ -18909,32 +18909,32 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N284" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="O284" t="n">
         <v>1</v>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -18974,12 +18974,12 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18989,11 +18989,11 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N285" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O285" t="n">
         <v>1</v>
@@ -19010,17 +19010,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C286" t="n">
         <v>5</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -19039,26 +19039,26 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N286" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O286" t="n">
         <v>1</v>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -19085,7 +19085,7 @@
         <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -19104,26 +19104,26 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N287" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -19318,7 +19318,7 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>CASE_005</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -19345,7 +19345,7 @@
         <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -19364,26 +19364,26 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>新易盛：2022年设立泰国基地，一二期已投产 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N291" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O293" t="n">
         <v>1</v>
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O294" t="n">
         <v>1</v>
@@ -19595,14 +19595,14 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C295" t="n">
         <v>4</v>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E295" t="n">
         <v>2</v>
@@ -19624,32 +19624,32 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N295" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O295" t="n">
         <v>1</v>
       </c>
       <c r="P295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -19689,26 +19689,26 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N296" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O296" t="n">
         <v>1</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -19790,14 +19790,14 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C298" t="n">
         <v>7</v>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E298" t="n">
         <v>2</v>
@@ -19819,32 +19819,32 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N298" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -19855,14 +19855,14 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C299" t="n">
         <v>8</v>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" t="n">
         <v>2</v>
@@ -19884,26 +19884,26 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -20033,7 +20033,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; TRD_003; CNGOV_001; UNCTAD_001</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; TRD_003; CNGOV_001; EU_003</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -20239,10 +20239,10 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -20251,11 +20251,11 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CASE_001; UNCTAD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; CNGOV_001; UNCTAD_001; IMF_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; KPMG_001; CNGOV_001; EU_003; CASE_010</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20397,10 +20397,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -20409,11 +20409,11 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; CNGOV_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_001; CASE_002; TRD_003; CNGOV_001</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; CNGOV_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_001; CASE_002; TRD_003; CNGOV_001</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001; CASE_008; CASE_007; TRD_003; UNCTAD_001; MOFCOM_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001; CASE_008; CASE_007; EU_003; MOFCOM_002; CASE_004</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20549,10 +20549,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -20561,11 +20561,11 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_001; TRD_003; UNCTAD_001; MOFCOM_001</t>
+          <t>CASE_010; CASE_001; EU_003; MOFCOM_002</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -20603,7 +20603,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; CASE_002; CASE_003; CASE_001; CASE_010; TRD_001</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; IRS_001; EU_003; CASE_003; UST_001; CASE_002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20630,10 +20630,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -20642,13 +20642,9 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>9</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>MOFCOM_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
         <v>2</v>
       </c>
@@ -20684,7 +20680,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; TRD_001; MOFCOM_002</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; IRS_001; UST_001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20765,7 +20761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; UNCTAD_001; CSIS_001; MOFCOM_001; WH_002</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001; ITA_001; CSIS_001; CASE_010; UST_001; EU_003</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20774,7 +20770,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -20792,10 +20788,10 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -20804,11 +20800,11 @@
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>UNCTAD_001; CSIS_001; MOFCOM_001; WH_002</t>
+          <t>CSIS_001; EU_003</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -20846,7 +20842,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; TRD_003; CASE_003; TRD_001; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; TRD_001; TRD_003; CASE_007; TRD_002</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20927,7 +20923,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001; CASE_001; CASE_009; MOFCOM_001; UNCTAD_001; MOFCOM_002</t>
+          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001; TRD_003; CASE_009; CASE_008; MOFCOM_002; EU_003</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20970,11 +20966,11 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>MOFCOM_001; UNCTAD_001</t>
+          <t>CASE_008; EU_003</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -21008,7 +21004,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001; TRD_001; TRD_003; KPMG_001; CASE_002; WTO_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001; IRS_001; CSIS_001; EU_003; UST_001; TRD_001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21051,7 +21047,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WEF_001; CASE_001; WTO_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; MCK_001; CSIS_001</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -21089,7 +21085,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; CASE_004; CASE_001; MOFCOM_001; CASE_005</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; CASE_005</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21122,7 +21118,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; CASE_004; CASE_001; MOFCOM_001; CASE_005</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; CASE_005</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -21160,7 +21156,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -21193,7 +21189,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -21231,7 +21227,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; CASE_003; TRD_001; CASE_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; CASE_003; IRS_001; CASE_002</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -21312,7 +21308,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; CASE_002; CASE_003; MOFCOM_002; WH_002; WH_001</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; CASE_002; UST_001; MOFCOM_002; CASE_003; IRS_001</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -21389,7 +21385,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003; CASE_002; CASE_010; UNCTAD_001; CSIS_001; CASE_007</t>
+          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002; CASE_010; IRS_001; CSIS_001; CASE_007</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -21416,10 +21412,10 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O17" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -21428,11 +21424,11 @@
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>WH_002; UNCTAD_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -21470,7 +21466,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; WH_001; UNCTAD_001; TRD_001; CASE_002; IMF_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001; WTO_001; CASE_002; CASE_008; UST_001; TRD_001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -21497,10 +21493,10 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -21509,11 +21505,11 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; UNCTAD_001; IMF_001</t>
+          <t>CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -21551,7 +21547,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001; MOFCOM_001; TRD_002; ITA_001; KPMG_001; CASE_007</t>
+          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001; IRS_001; EU_003; TRD_002; MOFCOM_002; CASE_007</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -21578,10 +21574,10 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -21590,11 +21586,11 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CASE_001; MOFCOM_001; TRD_002; ITA_001</t>
+          <t>CASE_001; TRD_002</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -21632,7 +21628,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003; CASE_007; CASE_006; CASE_005; CNGOV_001; MOFCOM_002</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004; CASE_007; CASE_006; CASE_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -21665,7 +21661,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003; CASE_007; CASE_006; CASE_005; CNGOV_001; MOFCOM_002</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004; CASE_007; CASE_006; CASE_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -21703,7 +21699,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001; TRD_001; CSIS_001; UNCTAD_001; TRD_002; CASE_003</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001; TRD_001; WTO_001; TRD_002; CASE_003; CASE_002</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -21712,7 +21708,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -21730,10 +21726,10 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -21742,11 +21738,11 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; UNCTAD_001</t>
+          <t>CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -21784,7 +21780,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; CASE_003; TRD_001; UNCTAD_001; TRD_002</t>
+          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; CASE_003; TRD_003; TRD_001; UST_001; TRD_002</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -21811,10 +21807,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -21823,11 +21819,11 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CSIS_001; UNCTAD_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -21865,7 +21861,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001; CASE_010; CASE_001; CASE_002; MOFCOM_002; CASE_008</t>
+          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001; CASE_003; CASE_010; UST_001; CASE_001; EU_003</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -21877,7 +21873,7 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0.75</v>
@@ -21892,10 +21888,10 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -21904,13 +21900,9 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>8</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>MOFCOM_001; CASE_008</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
         <v>2</v>
       </c>
@@ -21946,7 +21938,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; WH_001; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; CSIS_001; WH_001; EU_001; TRD_002; TRD_001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -21989,7 +21981,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>WH_002; CSIS_001</t>
+          <t>CSIS_001; EU_001</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -22027,7 +22019,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_003; CASE_008; CASE_003; TRD_001; CASE_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; CASE_003; EU_001; CASE_001; TRD_003</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -22054,10 +22046,10 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -22066,11 +22058,11 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CSIS_001; CASE_008</t>
+          <t>CSIS_001; CASE_008; EU_001</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -22108,7 +22100,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -22117,10 +22109,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -22141,7 +22133,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -22179,7 +22171,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001; MOFCOM_002; CASE_003; WTO_001; CASE_010; MOFCOM_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002; CASE_003; CASE_010; IRS_001; EU_003</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -22206,10 +22198,10 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -22218,11 +22210,11 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>WTO_001; MOFCOM_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -22260,7 +22252,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; TRD_003; CSIS_001; CASE_008; CASE_007</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -22341,7 +22333,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003; CASE_010; CSIS_001; WTO_001; WH_001; UNCTAD_001</t>
+          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002; DOC_001; CSIS_001; WH_001; WTO_001; CASE_008</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -22350,28 +22342,28 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.75</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -22380,11 +22372,11 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; CSIS_001; WTO_001; UNCTAD_001</t>
+          <t>CASE_003; DOC_001; CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -22422,7 +22414,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001; TRD_003; CASE_008; CASE_004; CASE_006; CASE_005</t>
+          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; CASE_008; CASE_004; CASE_006; EU_003</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -22434,7 +22426,7 @@
         <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0.6</v>
@@ -22455,11 +22447,11 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001; TRD_003; CASE_008; CASE_004; CASE_006; CASE_005</t>
+          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; CASE_008; CASE_004; CASE_006; EU_003</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -22493,7 +22485,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_001; TRD_003; CASE_003; CSIS_001; CASE_002; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CSIS_001; CASE_002; TRD_001; TRD_002; TRD_003; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -22502,10 +22494,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0.571</v>
@@ -22621,7 +22613,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -22651,7 +22643,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.885</v>
+        <v>0.921</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -22681,7 +22673,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.771</v>
+        <v>0.842</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -22782,7 +22774,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>0.867 / 0.887 / 5</t>
+          <t>0.867 / 0.925 / 5</t>
         </is>
       </c>
     </row>
@@ -22793,11 +22785,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>0.917 / 0.9 / 5</t>
+          <t>0.917 / 0.925 / 5</t>
         </is>
       </c>
     </row>
@@ -22812,7 +22804,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.91 / 0.906 / 10</t>
+          <t>0.91 / 0.925 / 10</t>
         </is>
       </c>
     </row>
@@ -22823,11 +22815,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>0.794 / 0.887 / 5</t>
+          <t>0.794 / 0.912 / 5</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22834,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>0.96 / 0.825 / 5</t>
+          <t>0.96 / 0.912 / 5</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/retrieval_results.xlsx
+++ b/data/evaluation/retrieval_results.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P401"/>
+  <dimension ref="A1:P431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3978,13 +3978,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O153" t="n">
         <v>1</v>
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
@@ -10495,14 +10495,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -10524,26 +10524,26 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
@@ -10560,14 +10560,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>5</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>2</v>
@@ -10589,26 +10589,26 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -14720,14 +14720,14 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C220" t="n">
         <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
         <v>2</v>
@@ -14749,17 +14749,17 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -14768,7 +14768,7 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -14814,12 +14814,12 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -20375,14 +20375,14 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C307" t="n">
         <v>6</v>
       </c>
       <c r="D307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" t="n">
         <v>2</v>
@@ -20404,26 +20404,26 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N307" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O307" t="n">
         <v>0</v>
@@ -20440,14 +20440,14 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C308" t="n">
         <v>7</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" t="n">
         <v>2</v>
@@ -20469,22 +20469,22 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N308" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -22484,26 +22484,26 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O339" t="n">
         <v>0</v>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>WTO_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -22549,22 +22549,22 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N340" t="n">
@@ -22585,14 +22585,14 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>WTO_003</t>
         </is>
       </c>
       <c r="C341" t="n">
         <v>10</v>
       </c>
       <c r="D341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341" t="n">
         <v>2</v>
@@ -22614,26 +22614,26 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - A notified body may subcontract activities or have activities carried ou...</t>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N341" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O341" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>EU_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -23914,22 +23914,22 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N361" t="n">
@@ -24925,7 +24925,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>EU_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -24954,17 +24954,17 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O377" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>EU_002</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -25019,17 +25019,17 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O378" t="n">
         <v>0</v>
@@ -25055,7 +25055,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -25084,17 +25084,17 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -25103,7 +25103,7 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O379" t="n">
         <v>0</v>
@@ -25120,17 +25120,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C380" t="n">
         <v>9</v>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -25149,22 +25149,22 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N380" t="n">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -25214,26 +25214,26 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N381" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O381" t="n">
         <v>0</v>
@@ -25315,14 +25315,14 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C383" t="n">
         <v>2</v>
       </c>
       <c r="D383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383" t="n">
         <v>2</v>
@@ -25344,22 +25344,22 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N383" t="n">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -25409,17 +25409,17 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O384" t="n">
         <v>1</v>
@@ -25445,7 +25445,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -25474,17 +25474,17 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -25539,17 +25539,17 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -25558,7 +25558,7 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O386" t="n">
         <v>1</v>
@@ -25575,14 +25575,14 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C387" t="n">
         <v>6</v>
       </c>
       <c r="D387" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E387" t="n">
         <v>2</v>
@@ -25604,32 +25604,32 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N387" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O387" t="n">
         <v>0</v>
       </c>
       <c r="P387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -25640,14 +25640,14 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C388" t="n">
         <v>7</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E388" t="n">
         <v>2</v>
@@ -25669,32 +25669,32 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N388" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O388" t="n">
         <v>0</v>
       </c>
       <c r="P388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -25734,17 +25734,17 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -25799,17 +25799,17 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O390" t="n">
         <v>0</v>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>EU_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -25864,17 +25864,17 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -25883,7 +25883,7 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O391" t="n">
         <v>0</v>
@@ -26539,6 +26539,1956 @@
         <v>0</v>
       </c>
       <c r="P401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="n">
+        <v>2</v>
+      </c>
+      <c r="E402" t="n">
+        <v>2</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>60</v>
+      </c>
+      <c r="O402" t="n">
+        <v>1</v>
+      </c>
+      <c r="P402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>2</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>38</v>
+      </c>
+      <c r="O403" t="n">
+        <v>1</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>3</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>2</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>34</v>
+      </c>
+      <c r="O404" t="n">
+        <v>1</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>4</v>
+      </c>
+      <c r="D405" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" t="n">
+        <v>2</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>战略与国际研究中心（CSIS）</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>31</v>
+      </c>
+      <c r="O405" t="n">
+        <v>1</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>5</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>1</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>30</v>
+      </c>
+      <c r="O406" t="n">
+        <v>1</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>6</v>
+      </c>
+      <c r="D407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E407" t="n">
+        <v>2</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>29</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>IEA_001</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>7</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>2</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>国际能源署（IEA）</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>28</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>8</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>2</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>26</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>9</v>
+      </c>
+      <c r="D410" t="n">
+        <v>1</v>
+      </c>
+      <c r="E410" t="n">
+        <v>2</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>26</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>10</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1</v>
+      </c>
+      <c r="E411" t="n">
+        <v>2</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>商务部</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>26</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="n">
+        <v>2</v>
+      </c>
+      <c r="E412" t="n">
+        <v>2</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>60</v>
+      </c>
+      <c r="O412" t="n">
+        <v>1</v>
+      </c>
+      <c r="P412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>2</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>2</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>33</v>
+      </c>
+      <c r="O413" t="n">
+        <v>1</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>3</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>2</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>31</v>
+      </c>
+      <c r="O414" t="n">
+        <v>1</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>4</v>
+      </c>
+      <c r="D415" t="n">
+        <v>1</v>
+      </c>
+      <c r="E415" t="n">
+        <v>2</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>29</v>
+      </c>
+      <c r="O415" t="n">
+        <v>1</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>5</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>28</v>
+      </c>
+      <c r="O416" t="n">
+        <v>1</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>6</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>2</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>26</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>IEA_001</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>7</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>2</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>国际能源署（IEA）</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>25</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>8</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>2</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>24</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>9</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1</v>
+      </c>
+      <c r="E420" t="n">
+        <v>2</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>23</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+      <c r="P420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>EU_002</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>10</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>2</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>23</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>EU_002</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D422" t="n">
+        <v>2</v>
+      </c>
+      <c r="E422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>50</v>
+      </c>
+      <c r="O422" t="n">
+        <v>1</v>
+      </c>
+      <c r="P422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>2</v>
+      </c>
+      <c r="D423" t="n">
+        <v>2</v>
+      </c>
+      <c r="E423" t="n">
+        <v>2</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>49</v>
+      </c>
+      <c r="O423" t="n">
+        <v>1</v>
+      </c>
+      <c r="P423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>3</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>2</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>38</v>
+      </c>
+      <c r="O424" t="n">
+        <v>1</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>4</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>35</v>
+      </c>
+      <c r="O425" t="n">
+        <v>1</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>5</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>2</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>33</v>
+      </c>
+      <c r="O426" t="n">
+        <v>1</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>6</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>2</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>32</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>7</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>2</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>30</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>8</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>30</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>9</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>2</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>29</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>10</v>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>2</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>商务部</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>29</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26553,7 +28503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -27099,7 +29049,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -27873,7 +29823,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -28341,7 +30291,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; UST_001; EU_003</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; MOFCOM_002; UST_001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -29038,7 +30988,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; IRS_001; TRD_001; WTO_003; CASE_002; EU_001</t>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; TRD_001; IRS_001; WTO_003; CASE_002; EU_001</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -29267,7 +31217,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; CASE_002; WTO_003; EU_001</t>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; TRD_001; CASE_002; WTO_003</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -29425,7 +31375,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003; MOFCOM_002; TSLA_001; EU_002</t>
+          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003; MOFCOM_002; TSLA_001; TRD_001</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -29583,7 +31533,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002; CASE_002; BIS_001; CASE_008; USMCA_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002; EU_002; CASE_002; BIS_001; TRD_001</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -29610,10 +31560,10 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -29622,13 +31572,9 @@
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>9</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>CASE_008</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
         <v>1.8</v>
       </c>
@@ -29664,7 +31610,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002; EU_002</t>
+          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -29676,7 +31622,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -29795,6 +31741,245 @@
         <v>2</v>
       </c>
       <c r="U41" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; UST_001; TRD_001; MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>8</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>CSIS_001; UST_001</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001; IRS_001; IEA_001; EU_001; UST_001; EU_002</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>AD/CVD; China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>9</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; DHS_001; EU_001; EU_003; CASE_002; IRS_001; SNE_001; TRD_001; MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>10</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -29843,7 +32028,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -29873,7 +32058,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -29888,7 +32073,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.915</v>
+        <v>0.921</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -29903,7 +32088,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -29933,7 +32118,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -29948,11 +32133,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>of 40; entity-free questions excluded</t>
+          <t>of 43; entity-free questions excluded</t>
         </is>
       </c>
     </row>
@@ -30045,11 +32230,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>0.94 / 0.967 / 7</t>
+          <t>0.948 / 0.957 / 8</t>
         </is>
       </c>
     </row>
@@ -30060,11 +32245,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.925 / 0.915 / 12</t>
+          <t>0.936 / 0.929 / 14</t>
         </is>
       </c>
     </row>
@@ -30090,7 +32275,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>

--- a/data/evaluation/retrieval_results.xlsx
+++ b/data/evaluation/retrieval_results.xlsx
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1525,14 +1525,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） - Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics i...</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1590,14 +1590,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1619,17 +1619,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） - Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics i...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3020,14 +3020,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - 122 Indonesia Investments, Holding Company for Indonesia's State-Owned M...</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -3085,14 +3085,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -3114,17 +3114,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - 122 Indonesia Investments, Holding Company for Indonesia's State-Owned M...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NIO_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>NIO_001</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>NIO Inc. Form 20-F（fiscal year ended December 31, 2025）蔚来2025财年年报 - Evidence ID: NIO_001 Title: NIO Inc. Form 20-F（fiscal year ended Decembe...</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -8964,22 +8964,22 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - 125 The Merchandise Exports from India Scheme (MEIS) provides duty r eba...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O133" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O135" t="n">
         <v>1</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O142" t="n">
         <v>1</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
@@ -10365,14 +10365,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -10394,32 +10394,32 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O153" t="n">
         <v>1</v>
       </c>
       <c r="P153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -10430,14 +10430,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
@@ -10459,32 +10459,32 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -10589,26 +10589,26 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -10654,26 +10654,26 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -11063,7 +11063,7 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O163" t="n">
         <v>1</v>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O172" t="n">
         <v>1</v>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O174" t="n">
         <v>1</v>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>5</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
@@ -11889,22 +11889,22 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N176" t="n">
@@ -11925,14 +11925,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -11954,26 +11954,26 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -12055,14 +12055,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>8</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -12084,17 +12084,17 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -12120,14 +12120,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>2</v>
@@ -12149,17 +12149,17 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -12575,17 +12575,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C187" t="n">
         <v>6</v>
       </c>
       <c r="D187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N187" t="n">
@@ -12629,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -12640,14 +12640,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C188" t="n">
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
         <v>2</v>
@@ -12669,17 +12669,17 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -12705,17 +12705,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C189" t="n">
         <v>8</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -12734,22 +12734,22 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18....</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N189" t="n">
@@ -12770,14 +12770,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>9</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" t="n">
         <v>1</v>
@@ -12799,12 +12799,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18....</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O192" t="n">
         <v>1</v>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O193" t="n">
         <v>1</v>
@@ -13225,14 +13225,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>6</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
         <v>2</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - disclosing certain foreign tax and global business identi- fiers; and pr...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -13355,14 +13355,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C199" t="n">
         <v>8</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" t="n">
         <v>2</v>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - disclosing certain foreign tax and global business identi- fiers; and pr...</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13403,13 +13403,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O203" t="n">
         <v>1</v>
@@ -14005,14 +14005,14 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>8</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
         <v>2</v>
@@ -14034,22 +14034,22 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -14070,14 +14070,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210" t="n">
         <v>2</v>
@@ -14099,26 +14099,26 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O214" t="n">
         <v>1</v>
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O256" t="n">
         <v>1</v>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -17739,22 +17739,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N266" t="n">
@@ -17775,14 +17775,14 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C267" t="n">
         <v>6</v>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E267" t="n">
         <v>2</v>
@@ -17804,12 +17804,12 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -17819,17 +17819,17 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -17840,14 +17840,14 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C268" t="n">
         <v>7</v>
       </c>
       <c r="D268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" t="n">
         <v>2</v>
@@ -17869,32 +17869,32 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
       </c>
       <c r="P268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -18148,7 +18148,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O272" t="n">
         <v>1</v>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -18324,17 +18324,17 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -18389,17 +18389,17 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O276" t="n">
         <v>1</v>
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -19838,7 +19838,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -20423,7 +20423,7 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O307" t="n">
         <v>0</v>
@@ -20830,7 +20830,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -20859,17 +20859,17 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -20924,17 +20924,17 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O316" t="n">
         <v>1</v>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -22503,7 +22503,7 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O339" t="n">
         <v>0</v>
@@ -23040,14 +23040,14 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C348" t="n">
         <v>7</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" t="n">
         <v>2</v>
@@ -23069,17 +23069,17 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -23105,14 +23105,14 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>EU_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C349" t="n">
         <v>8</v>
       </c>
       <c r="D349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E349" t="n">
         <v>2</v>
@@ -23134,17 +23134,17 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -23153,7 +23153,7 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O349" t="n">
         <v>0</v>
@@ -23170,14 +23170,14 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C350" t="n">
         <v>9</v>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E350" t="n">
         <v>2</v>
@@ -23199,17 +23199,17 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -23218,7 +23218,7 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O350" t="n">
         <v>0</v>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_002</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -23264,17 +23264,17 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -23283,7 +23283,7 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O351" t="n">
         <v>0</v>
@@ -25315,14 +25315,14 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C383" t="n">
         <v>2</v>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E383" t="n">
         <v>2</v>
@@ -25344,22 +25344,22 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N383" t="n">
@@ -25380,14 +25380,14 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>3</v>
       </c>
       <c r="D384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E384" t="n">
         <v>2</v>
@@ -25409,26 +25409,26 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N384" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O384" t="n">
         <v>1</v>
@@ -27005,14 +27005,14 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C409" t="n">
         <v>8</v>
       </c>
       <c r="D409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E409" t="n">
         <v>2</v>
@@ -27034,26 +27034,26 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N409" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O409" t="n">
         <v>0</v>
@@ -27070,14 +27070,14 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C410" t="n">
         <v>9</v>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E410" t="n">
         <v>2</v>
@@ -27099,22 +27099,22 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N410" t="n">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001; WB_001; CASE_001; CASE_008; CASE_004</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001; CASE_008; CASE_004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -28897,7 +28897,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; WTO_004</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; WTO_004; TRD_003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -28930,7 +28930,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; WTO_004</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; WTO_004; TRD_003</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -29203,7 +29203,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001; ITA_001; FR_001; XPEV_001; DHS_001; UST_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; ITA_001; NIO_001; FR_001; XPEV_001; DHS_001; UST_001</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; WTO_002</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -29627,7 +29627,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; WTO_002</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002; TRD_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001; IRS_001; CASE_001; EU_003; TSLA_001; SNE_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001; TRD_001; CASE_001; TSLA_001; EU_003; SNE_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -29993,7 +29993,7 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0.8</v>
@@ -30062,7 +30062,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; CASE_004; TSLA_001; DHS_001; CASE_007; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; TSLA_001; DHS_001; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -30095,7 +30095,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; CASE_004; TSLA_001; DHS_001; CASE_007; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; TSLA_001; DHS_001; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001; USMCA_001; WH_001; CASE_010; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; TRD_003; DHS_001; TRD_001</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; DHS_001; TRD_003; TRD_001</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; USMCA_001; DHS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; CSIS_001; TRD_003; CASE_008; USMCA_001; DHS_001</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -31065,7 +31065,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001; MOFCOM_001; BIS_002; CASE_009; BIS_001; LI_001</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001; MOFCOM_001; BIS_002; BIS_001; CASE_009; LI_001</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -31294,7 +31294,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004; CASE_001; EU_003; EU_002; MOFCOM_002; CNGOV_001</t>
+          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004; CASE_001; ITA_001; EU_003; FR_001; EU_002</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -31321,10 +31321,10 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -31333,11 +31333,11 @@
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; WTO_004; EU_002; MOFCOM_002; CNGOV_001</t>
+          <t>DHS_001; IRS_001; WTO_004; ITA_001; EU_002</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -31772,7 +31772,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; UST_001; TRD_001; MOFCOM_002</t>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; TRD_001; UST_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -32058,7 +32058,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.867</v>
+        <v>0.869</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.936 / 0.929 / 14</t>
+          <t>0.936 / 0.933 / 14</t>
         </is>
       </c>
     </row>
@@ -32275,7 +32275,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.714</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
